--- a/Дело3а-78-2026Таганай/11_Поставщики/00_Ведомость_11_Поставщики_(агрегат).xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/00_Ведомость_11_Поставщики_(агрегат).xlsx
@@ -21,7 +21,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="DD.MM.YYYY"/>
+    <numFmt numFmtId="165" formatCode="dd.mm.yyyy"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -633,11 +633,11 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>255.69 МБ</t>
+          <t>255.68 МБ</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>46157.92972310467</v>
+        <v>46157.93550779713</v>
       </c>
     </row>
     <row r="9">
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="E33" s="13" t="n">
-        <v>46157.92525228093</v>
+        <v>46157.93536035729</v>
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>

--- a/Дело3а-78-2026Таганай/11_Поставщики/00_Ведомость_11_Поставщики_(агрегат).xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/00_Ведомость_11_Поставщики_(агрегат).xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ведомость 11" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ведомость 11'!$B$11:$H$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ведомость 11'!$B$11:$H$33</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Ведомость 11'!$1:$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -128,8 +128,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8F4EC"/>
-        <bgColor rgb="00E8F4EC"/>
+        <fgColor rgb="00FFF6CC"/>
+        <bgColor rgb="00FFF6CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -568,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H42"/>
+  <dimension ref="B2:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
@@ -633,11 +633,11 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>255.68 МБ</t>
+          <t>255.64 МБ</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>46157.93550779713</v>
+        <v>46158.29724296797</v>
       </c>
     </row>
     <row r="9">
@@ -1429,20 +1429,20 @@
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Сводная ведомость</t>
+          <t>Сводная ведомость поставщиков</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Сводная_ведомость.xlsx</t>
+          <t>Сводная_ведомость_поставщиков.xlsx</t>
         </is>
       </c>
       <c r="E33" s="13" t="n">
-        <v>46157.93536035729</v>
+        <v>46157.75173269795</v>
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>
-          <t>51 КБ</t>
+          <t>14 КБ</t>
         </is>
       </c>
       <c r="G33" s="17" t="inlineStr"/>
@@ -1452,85 +1452,54 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="32" customHeight="1">
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>11.23</t>
-        </is>
-      </c>
-      <c r="C34" s="11" t="inlineStr">
-        <is>
-          <t>Сводная ведомость поставщиков</t>
-        </is>
-      </c>
-      <c r="D34" s="12" t="inlineStr">
-        <is>
-          <t>Сводная_ведомость_поставщиков.xlsx</t>
-        </is>
-      </c>
-      <c r="E34" s="13" t="n">
-        <v>46157.75173269795</v>
-      </c>
-      <c r="F34" s="14" t="inlineStr">
-        <is>
-          <t>14 КБ</t>
-        </is>
-      </c>
-      <c r="G34" s="17" t="inlineStr"/>
-      <c r="H34" s="16" t="inlineStr">
-        <is>
-          <t>_____________</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="18" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="18" t="inlineStr">
         <is>
           <t>Председатель правления РКООИ ЦИП «Таганай»: Богдановский С.В.    ____________________</t>
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="B38" s="19" t="inlineStr">
+        <is>
+          <t>Подсказки:</t>
+        </is>
+      </c>
+    </row>
     <row r="39">
-      <c r="B39" s="19" t="inlineStr">
-        <is>
-          <t>Подсказки:</t>
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>• Колонка «Наименование документа» заполнена автоматически по имени файла — проверьте формулировки.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="20" t="inlineStr">
         <is>
-          <t>• Колонка «Наименование документа» заполнена автоматически по имени файла — проверьте формулировки.</t>
+          <t>• Колонка «Стр.» (G) — для PDF укажите число страниц при необходимости.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="20" t="inlineStr">
         <is>
-          <t>• Колонка «Стр.» (G) — для PDF укажите число страниц при необходимости.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="20" t="inlineStr">
-        <is>
           <t>• Перезапуск скрипта перезапишет файл (в т.ч. наименования).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B11:H34"/>
+  <autoFilter ref="B11:H33"/>
   <mergeCells count="10">
+    <mergeCell ref="B36:H36"/>
     <mergeCell ref="E9:H9"/>
     <mergeCell ref="B40:H40"/>
     <mergeCell ref="B41:H41"/>
     <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B39:H39"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B42:H42"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="B5:H5"/>
-    <mergeCell ref="B37:H37"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/Дело3а-78-2026Таганай/11_Поставщики/00_Ведомость_11_Поставщики_(агрегат).xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/00_Ведомость_11_Поставщики_(агрегат).xlsx
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>46158.29724296797</v>
+        <v>46158.37381774843</v>
       </c>
     </row>
     <row r="9">
